--- a/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N26_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T7861_W0026F0002T0006Z000C1N26_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>36.98167924234627</v>
+        <v>6.009522876881269</v>
       </c>
       <c r="D2" t="n">
-        <v>37.45392980604315</v>
+        <v>6.086263593482012</v>
       </c>
       <c r="E2" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F2" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>25.03483882878048</v>
+        <v>4.068161309676827</v>
       </c>
       <c r="D3" t="n">
-        <v>25.13755456804174</v>
+        <v>4.084852617306783</v>
       </c>
       <c r="E3" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F3" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>14.63977178061423</v>
+        <v>2.378962914349812</v>
       </c>
       <c r="D4" t="n">
-        <v>15.03063605857897</v>
+        <v>2.442478359519082</v>
       </c>
       <c r="E4" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F4" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>13.43495346820551</v>
+        <v>2.183179938583395</v>
       </c>
       <c r="D5" t="n">
-        <v>12.94620773732834</v>
+        <v>2.103758757315856</v>
       </c>
       <c r="E5" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F5" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.11696089096434</v>
+        <v>3.431506144781705</v>
       </c>
       <c r="D6" t="n">
-        <v>20.26159055320143</v>
+        <v>3.292508464895233</v>
       </c>
       <c r="E6" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F6" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>27.14939957126944</v>
+        <v>4.411777430331284</v>
       </c>
       <c r="D7" t="n">
-        <v>38.01822830861101</v>
+        <v>6.17796210014929</v>
       </c>
       <c r="E7" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F7" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>39.1488676206048</v>
+        <v>6.36169098834828</v>
       </c>
       <c r="D8" t="n">
-        <v>38.21723455128477</v>
+        <v>6.210300614583775</v>
       </c>
       <c r="E8" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F8" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>21.60463345987424</v>
+        <v>3.510752937229565</v>
       </c>
       <c r="D9" t="n">
-        <v>43.3893696050394</v>
+        <v>7.050772560818903</v>
       </c>
       <c r="E9" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F9" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>20.97881070791259</v>
+        <v>3.409056740035795</v>
       </c>
       <c r="D10" t="n">
-        <v>20.0665580974055</v>
+        <v>3.260815690828395</v>
       </c>
       <c r="E10" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F10" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>11.89580543450159</v>
+        <v>1.933068383106509</v>
       </c>
       <c r="D11" t="n">
-        <v>45.93135938075489</v>
+        <v>7.46384589937267</v>
       </c>
       <c r="E11" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F11" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>42.08569707124846</v>
+        <v>6.838925774077875</v>
       </c>
       <c r="D12" t="n">
-        <v>41.2950250803538</v>
+        <v>6.710441575557494</v>
       </c>
       <c r="E12" t="n">
-        <v>9.98087214557402</v>
+        <v>1.621891723655778</v>
       </c>
       <c r="F12" t="n">
-        <v>11.57837714965486</v>
+        <v>1.881486286818914</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
